--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137155406</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137155406</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137155406</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137155406</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137155406</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 2197-2025 artfynd.xlsx
+++ b/artfynd/A 2197-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137155379</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137155405</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137155376</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137155381</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137155404</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137155407</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137155414</v>
       </c>
       <c r="B8" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137155416</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137155415</v>
       </c>
       <c r="B10" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137155406</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
